--- a/www/download/COUNTRY.NLD.rpO1.xlsx
+++ b/www/download/COUNTRY.NLD.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>Países Baixos</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.727939807997103</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.764759852979333</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>0.884290610900269</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>0.89893298342352</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.938262380158969</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>1.08271977415814</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>1.11656987220386</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>1.05752964058676</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>0.884017009417596</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.803923183139281</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.803793923183733</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.796431999730865</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>0.729660724026465</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.679902074187573</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948694066692</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7.155</t>
+          <t>2.5446621291707</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7.315</t>
+          <t>2.46934980792738</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>7.541</t>
+          <t>2.35322513253852</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7.738</t>
+          <t>2.31798961661069</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7.937</t>
+          <t>2.44822630415783</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8.115</t>
+          <t>2.29161838665584</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8.282</t>
+          <t>2.17951985499898</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>8.324</t>
+          <t>2.21590073992427</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8.283</t>
+          <t>2.57215892013288</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>8.211</t>
+          <t>2.29134168404803</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>8.252</t>
+          <t>2.31963958832513</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>8.392</t>
+          <t>2.25356531433525</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>8.607</t>
+          <t>2.30115753253666</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>8.738</t>
+          <t>2.15827182259862</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>8.694</t>
+          <t>2.10212371898151</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6.014</t>
+          <t>3.5717972569861</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>3.42836464485765</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>6.354</t>
+          <t>3.37139792416807</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>6.565</t>
+          <t>3.35422804863335</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>3.58049454626387</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>6.988</t>
+          <t>3.40734941518927</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7.152</t>
+          <t>3.30323746373205</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>7.199</t>
+          <t>3.40301825666035</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>7.167</t>
+          <t>3.78328402465623</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>7.083</t>
+          <t>3.49409939543916</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>7.105</t>
+          <t>3.5657775233261</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>7.227</t>
+          <t>3.47970750156999</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>7.425</t>
+          <t>3.28375503299014</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>7.55</t>
+          <t>3.28529936718651</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>7.473</t>
+          <t>3.20272566407948</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10445.244</t>
+          <t>4.32878246667599</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10702.777</t>
+          <t>4.23932385153359</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10961.388</t>
+          <t>4.16602756730542</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>11146.709</t>
+          <t>4.19896596946922</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>11403.058</t>
+          <t>4.46868170283391</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>11641.135</t>
+          <t>4.31707669470152</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>11791.079</t>
+          <t>4.16839166049094</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>11723.033</t>
+          <t>4.38876979404761</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>11603.664</t>
+          <t>3.6766391391069</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>11489.169</t>
+          <t>4.49019062773815</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>11496.405</t>
+          <t>4.54642918311654</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>11679.322</t>
+          <t>4.43506187226697</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>11950.122</t>
+          <t>4.21527999483203</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>12164.649</t>
+          <t>4.04863970672779</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>12042.709</t>
+          <t>3.9393863580278</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>8502.439</t>
+          <t>16617183697930.3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8679.178</t>
+          <t>14719655264060.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>8931.979</t>
+          <t>13858698507869.9</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>9176.159</t>
+          <t>15826145023772</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>9443.354</t>
+          <t>17199577861453.1</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>9648.194</t>
+          <t>18516347092995.6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>9833.376</t>
+          <t>20063132782962.2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9812.115</t>
+          <t>21003094633117.9</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>9726.175</t>
+          <t>24350821770600.7</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>9580.306</t>
+          <t>23147563351231.2</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>9554.199</t>
+          <t>21297388799878.2</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>9704.286</t>
+          <t>19438913914764.6</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>9945.624</t>
+          <t>16778922922273</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>10062.514</t>
+          <t>13914962517372.6</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>9905.508</t>
+          <t>12329680199837.9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20.34</t>
+          <t>3841095849573.39</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>21.77</t>
+          <t>3406197833419.23</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24.61</t>
+          <t>3199765171635.69</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>3756401621571.63</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>4108232702326.84</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>25.83</t>
+          <t>4325992705517.84</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>25.1</t>
+          <t>4810690154911.07</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>5134134828532.54</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>28.35</t>
+          <t>5998431572501.55</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>5567933082302</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>5022548840364.7</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>33.37</t>
+          <t>4515161601476.83</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>3903731371279.56</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>33.37</t>
+          <t>3297859935854.6</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>33.96</t>
+          <t>3082993060143.15</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>47.23</t>
+          <t>844339118.21027</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>47.65</t>
+          <t>754019533.646412</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>46.6</t>
+          <t>772986090.705324</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>46.69</t>
+          <t>854721360.805652</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>45.64</t>
+          <t>927320449.275941</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>43.9</t>
+          <t>1044995963.63759</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>44.32</t>
+          <t>1117420063.62696</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>45.28</t>
+          <t>1091944251.33719</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>41.08</t>
+          <t>1044176054.37706</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>870466840.33523</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>756859954.875281</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>42.73</t>
+          <t>638533468.744298</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>469550918.208936</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>339695949.644624</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>41.48</t>
+          <t>346910300.994081</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>442432.003995339</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>442009.158975831</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>410605.257385623</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>29.33</t>
+          <t>435488.986505776</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>448600.353435524</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>422872.10990973</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>30.58</t>
+          <t>442074.25322783</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>27.36</t>
+          <t>496800.457689094</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>616390.156955768</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>702195.211113388</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>712538.347873183</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>23.89</t>
+          <t>742314.076188473</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>23.98</t>
+          <t>849674.157739217</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>24.86</t>
+          <t>962664.691582599</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>948952.413160471</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>747053.451819222</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>16.55</t>
+          <t>743279.811296978</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>685104.153219837</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>18.11</t>
+          <t>710003.487665174</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20.74</t>
+          <t>719260.588712763</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>682748.109295269</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>699529.232453708</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>20.05</t>
+          <t>765641.61008817</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>22.69</t>
+          <t>932700.78676433</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>1065634.02828634</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>25.13</t>
+          <t>1097506.94789856</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>25.01</t>
+          <t>1161988.60786549</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>1337561.79118063</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>1477878.14736793</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>1363346.36200214</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>46.73</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>3.34948286612085</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>46.61</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>46.73</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>46.41</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>43.86</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>44.34</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>45.93</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>44.78</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>44.52</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>44.64</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>45.36</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>110051.613121773</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>36.13</t>
+          <t>108526.400879063</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>34.86</t>
+          <t>97134.9665358162</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>35.16</t>
+          <t>98288.8959109143</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>32.86</t>
+          <t>96451.8829182127</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>85897.808974582</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>37.41</t>
+          <t>81554.2305194016</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>34.02</t>
+          <t>83885.6830009321</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>103258.202894404</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>30.88</t>
+          <t>113762.028194282</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>30.23</t>
+          <t>113955.845160289</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>30.31</t>
+          <t>119046.714460891</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>29.74</t>
+          <t>131248.655510072</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>30.17</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.727939807997103</t>
+          <t>638686.518426151</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.764759852979333</t>
+          <t>553818.726346066</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.884290610900269</t>
+          <t>503557.211623597</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.89893298342352</t>
+          <t>572184.16352171</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262380158969</t>
+          <t>603254.615462654</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271977415814</t>
+          <t>619044.612716943</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656987220386</t>
+          <t>672637.905232214</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752964058676</t>
+          <t>713177.296238976</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017009417596</t>
+          <t>836897.225518583</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923183139281</t>
+          <t>786058.958561292</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793923183733</t>
+          <t>706879.448616128</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796431999730865</t>
+          <t>624736.551380747</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.729660724026465</t>
+          <t>525776.66439895</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902074187573</t>
+          <t>436778.285059151</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948694066692</t>
+          <t>412574.774848907</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>339575204961.27</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>268799426963.312</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>350782016348.759</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>352117485080.031</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>317144572411.584</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>460800027082.07</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>613949657056.76</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>414726291077.766</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>430896786536.674</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>519172881295.257</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>832773623943.749</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>838459710677.048</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>808970526598.659</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>938180809581.202</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.418</t>
+          <t>359598621167.377</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>762984810814.338</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>663836952568.043</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>730867339840.719</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>821205217080.214</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.247</t>
+          <t>804071611362.928</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>982175977040.416</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>1058654151788.29</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>887620702926.507</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>999721089381.214</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>982930442924.564</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>1186550713736.22</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>1204192223643.57</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>1048184060304.17</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>1119399159052.2</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>537481415466.146</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.496</t>
+          <t>-423409605853.067</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.478</t>
+          <t>-395037525604.731</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>-380085323491.96</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>-469087732000.183</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.344</t>
+          <t>-486927038951.343</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.237</t>
+          <t>-521375949958.346</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.269</t>
+          <t>-444704494731.53</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.386</t>
+          <t>-472894411848.741</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.721</t>
+          <t>-568824302844.54</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1.941</t>
+          <t>-463757561629.307</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>1.998</t>
+          <t>-353777089792.469</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2.107</t>
+          <t>-365732512966.524</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2.389</t>
+          <t>-239213533705.509</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-181218349470.998</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-177882794298.769</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>2862898.03718876</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>2408825.06117909</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>2133712.09605089</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>2411451.97382896</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>2622426.13366813</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>2638340.9831704</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>2789590.30599383</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.822</t>
+          <t>2999717.81158263</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.998</t>
+          <t>3618785.36822622</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.135</t>
+          <t>3300442.03450147</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>2988101.75387069</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.281</t>
+          <t>2588009.0540404</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.486</t>
+          <t>2129657.96080544</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.692</t>
+          <t>1725167.20922234</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.522</t>
+          <t>1595274.61321646</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.379</t>
+          <t>2901643.13349764</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>2551793.90027561</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>2373216.96683746</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>2731170.44649478</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.367</t>
+          <t>2959843.70803498</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>3113287.05431164</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>3395799.58353633</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>3603519.41721145</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>4257635.91971176</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>4074037.31964893</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.568</t>
+          <t>3695581.50093219</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>3294254.49739732</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>2787332.46406935</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.779</t>
+          <t>2326475.60947605</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.711</t>
+          <t>2204063.9924821</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>254.47</t>
+          <t>218027.084282411</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>246.93</t>
+          <t>217152.718214827</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>235.32</t>
+          <t>206768.148740123</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>231.8</t>
+          <t>207986.069925308</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>244.82</t>
+          <t>212322.094138053</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>229.16</t>
+          <t>214498.067189643</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>217.95</t>
+          <t>210812.087293922</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>221.59</t>
+          <t>222189.914982798</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>257.22</t>
+          <t>266519.660973371</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>229.13</t>
+          <t>313839.379246555</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>231.96</t>
+          <t>341871.736434771</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>225.36</t>
+          <t>374203.809168873</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>230.12</t>
+          <t>436276.695560478</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>215.83</t>
+          <t>527855.087696026</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>210.21</t>
+          <t>431915.949944875</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>357.18</t>
+          <t>6131329109575.7</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>342.84</t>
+          <t>5379900449999.82</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>337.14</t>
+          <t>5164064509816.95</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>335.42</t>
+          <t>5730585487226.83</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>358.05</t>
+          <t>6253079612472.77</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>340.73</t>
+          <t>7030393003697.95</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>330.32</t>
+          <t>7153371532794.22</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>340.3</t>
+          <t>7440512218495.81</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>378.33</t>
+          <t>8454761902303.88</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>349.41</t>
+          <t>8138938509031.96</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>356.58</t>
+          <t>7634955101755.09</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>347.97</t>
+          <t>7037337747221.41</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>328.38</t>
+          <t>6054241651905.72</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>328.53</t>
+          <t>5205568473327.76</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>320.27</t>
+          <t>4394172329964.68</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>432.88</t>
+          <t>183512.62021827</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>423.93</t>
+          <t>184335.763393688</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>416.6</t>
+          <t>174567.50063862</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>419.9</t>
+          <t>178706.421023756</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>446.87</t>
+          <t>184993.302417061</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>431.71</t>
+          <t>183369.48791768</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>416.84</t>
+          <t>178768.266007625</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>438.88</t>
+          <t>184656.766492686</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>367.66</t>
+          <t>222165.962424287</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>449.02</t>
+          <t>257878.856784458</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>454.64</t>
+          <t>276263.221877456</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>443.51</t>
+          <t>309369.256717158</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>421.53</t>
+          <t>357993.67823002</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>404.86</t>
+          <t>438605.723588208</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>393.94</t>
+          <t>362207.699963329</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20761175.374</t>
+          <t>5211231851953.52</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>18665910.506</t>
+          <t>4580678826346.36</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17897335.716</t>
+          <t>4441417356130.01</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>21134351.343</t>
+          <t>4984677918892.92</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>23492110.8</t>
+          <t>5466764198431.87</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>25265834.39</t>
+          <t>6074735551776.47</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>28125380.658</t>
+          <t>6199336310389.89</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>29995400.14</t>
+          <t>6084603503998.48</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>35266526.27</t>
+          <t>6914732412929.83</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>33453158.939</t>
+          <t>6618377924734.47</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>30494441.835</t>
+          <t>6341762827860.36</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>27646530.143</t>
+          <t>6084677399486.88</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>23989405.413</t>
+          <t>5270888948068.21</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>20327728.637</t>
+          <t>4801922659366.1</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>19161062.465</t>
+          <t>3722519765584.08</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>17217626.255</t>
+          <t>34514.46406414</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>14815199.115</t>
+          <t>32816.9548211389</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>13558295.847</t>
+          <t>32200.6481015032</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>15831235.26</t>
+          <t>29279.6489015525</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>17859020.927</t>
+          <t>27328.7917209921</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>18437191.138</t>
+          <t>31128.5792719626</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>19951082.918</t>
+          <t>32043.8212862972</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>21594848.537</t>
+          <t>37533.148490112</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>25937517.469</t>
+          <t>44353.698549084</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>23378195.986</t>
+          <t>55960.5224620967</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>21231183.094</t>
+          <t>65608.5145573149</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>18704330.776</t>
+          <t>64834.5524517154</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>15812060.813</t>
+          <t>78283.0173304588</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>13025738.725</t>
+          <t>89249.364107818</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>11920798.026</t>
+          <t>69708.2499815464</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>16617183.698</t>
+          <t>920097257622.175</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>14719655.264</t>
+          <t>799221623653.454</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>13858698.508</t>
+          <t>722647153686.945</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>15826145.024</t>
+          <t>745907568333.914</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>17199577.861</t>
+          <t>786315414040.907</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>18516347.093</t>
+          <t>955657451921.483</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>20063132.783</t>
+          <t>954035222404.331</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>21003094.633</t>
+          <t>1355908714497.33</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>24350821.771</t>
+          <t>1540029489374.06</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>23147563.351</t>
+          <t>1520560584297.49</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>21297388.8</t>
+          <t>1293192273894.74</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>19438913.915</t>
+          <t>952660347734.527</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>16778922.922</t>
+          <t>783352703837.512</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>13914962.517</t>
+          <t>403645813961.669</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>12329680.2</t>
+          <t>671652564380.608</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.747</t>
+          <t>176167.03781</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>170677.10748</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>154661.82466</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>157627.99106</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>156102.38865</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>147529.40157</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>152020.04329</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.766</t>
+          <t>167422.26007</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.933</t>
+          <t>206325.21695</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.066</t>
+          <t>232158.99726</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.098</t>
+          <t>242511.16397</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.162</t>
+          <t>258749.02057</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>1.338</t>
+          <t>298198.86517</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1.478</t>
+          <t>339593.02174</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>306192.06371</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>9841295.648</t>
+          <t>0.00926182820121817</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>8753395.888</t>
+          <t>0.00946094273200262</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>8305969.89</t>
+          <t>0.0143453224076314</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>9707152.115</t>
+          <t>0.0154200939004321</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>10727317.51</t>
+          <t>0.0176829078484975</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>11468426.871</t>
+          <t>0.0240092721571757</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>12679090.495</t>
+          <t>0.029176592346844</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>13628239.23</t>
+          <t>0.032637340433184</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>16092628.061</t>
+          <t>0.0317097065865428</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>15252992.775</t>
+          <t>0.0335598035793418</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>13826979.646</t>
+          <t>0.0414849392891144</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>12418176.329</t>
+          <t>0.0440483637487281</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>10658660.628</t>
+          <t>0.0482763596637239</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>9063969.938</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>8582030.293</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>214079.514468347</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>211595.833904053</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>193626.391223694</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>204747.186797824</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.449</t>
+          <t>210329.226889465</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>195621.254394251</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>203650.489479185</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>225832.914828991</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.616</t>
+          <t>277994.651057547</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.702</t>
+          <t>312256.202294237</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.713</t>
+          <t>316701.821837909</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>332639.823540857</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>384163.475688043</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.963</t>
+          <t>434081.231334496</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.949</t>
+          <t>417675.806562603</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3841095.85</t>
+          <t>254812.107116176</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3406197.833</t>
+          <t>252872.209196045</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>3199765.172</t>
+          <t>230613.67452377</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>3756401.622</t>
+          <t>241436.717045849</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4108232.702</t>
+          <t>246776.722249077</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4325992.706</t>
+          <t>229293.949001612</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4810690.155</t>
+          <t>237472.510775032</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>5134134.829</t>
+          <t>262702.819050097</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>5998431.573</t>
+          <t>323233.238782572</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>5567933.082</t>
+          <t>364523.867293859</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>5022548.84</t>
+          <t>370710.693728264</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>4515161.601</t>
+          <t>389610.62877315</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>3903731.371</t>
+          <t>449130.385402166</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3297859.936</t>
+          <t>507293.478975141</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3082993.06</t>
+          <t>488282.846078824</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>1496157.71432994</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>1478277.10103172</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>1317570.51764548</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>1344462.34031398</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>1343875.25775235</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>1236786.42357057</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>1268976.89371771</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>1386250.90826854</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>1720549.65296268</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>1941061.64441195</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>1997579.77597407</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>2106550.71809876</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>2389477.35353878</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>844.339</t>
+          <t>254812.107116176</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>754.02</t>
+          <t>263395.628118059</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>772.986</t>
+          <t>271597.527540224</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>854.721</t>
+          <t>283391.754634822</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>927.32</t>
+          <t>296372.924171784</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1044.996</t>
+          <t>307233.977882562</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1117.42</t>
+          <t>313823.072770171</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1091.944</t>
+          <t>313332.213441468</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1044.176</t>
+          <t>315037.119696603</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>870.467</t>
+          <t>322971.516033075</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>756.86</t>
+          <t>323774.00346502</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>638.533</t>
+          <t>334532.029794109</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>469.551</t>
+          <t>350683.5963835</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>339.696</t>
+          <t>367108.493360462</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>346.91</t>
+          <t>371617.068337142</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>214079.514468347</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>220585.102493354</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>228505.739959758</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>240711.598582331</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>252303.567449044</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>261847.057393588</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>269401.940246859</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>269113.367741665</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>270383.886646088</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>275350.60699783</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>275277.742056614</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>285522.614991753</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>299766.400232008</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>313096.873516325</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>315879.92168012</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>123908.768833824</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>122512.295873955</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>116035.94040623</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>119020.631444151</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>120215.505260923</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>115592.150818388</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>118578.652044968</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>129129.225819903</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>157816.327557428</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>178903.675716141</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>196825.320891736</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>211836.82674685</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>246603.923637834</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>271228.928544859</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>222533.708471176</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>17217626255045.3</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>14815199115074.9</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>13558295847314.4</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>15831235260130.5</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>17859020926859.2</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>18437191138407.8</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>19951082918300.5</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>21594848536870.9</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>25937517469273.5</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>23378195986412.1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>21231183093774</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>18704330776311.4</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>15812060813302.4</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>13025738725023.8</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>11920798025933.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>20761175374167.9</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>18665910505820.1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>17897335715802.6</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>21134351342577.2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>23492110799582.3</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>25265834389960.3</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>28125380658080.1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>29995400140275.9</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>35266526269826.5</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>33453158938982.6</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>30494441835184.6</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>27646530142723.4</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>23989405413274.9</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>20327728636900.5</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>19161062465377.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>9841295648029.58</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>8753395887786.42</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>8305969889555.89</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>9707152114647.21</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>10727317510053.3</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>11468426871394.9</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>12679090495372.1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>13628239229864.7</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>16092628060551.9</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>15252992774936.9</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>13826979645581.8</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>12418176328985.2</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>10658660628433.2</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>9063969938270.55</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>8582030293424.93</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>7154972</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>7314819</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>7541382</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>7738203</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>7936943</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>8115485</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>8282403</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>8323918</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>8283124</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>8211304</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>8251595</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>8392348</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>8606582</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>8737563.61515372</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>8693514.58520918</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>6014055</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>6150384</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>6354323</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>6565022</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>6810114</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>6988176</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>7151976</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>7198960</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>7167465</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>7083353</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>7105241</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>7227305</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>7424695</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>7550421</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>7472568</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>10445244203.6327</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>10702776704.0685</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>10961388159.0455</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>11146708726.7442</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>11403058040.3236</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>11641134545.9245</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>11791078936</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>11723033019</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>11603663726</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>11489168633</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>11496405247</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>11679322035</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>11950121943</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>12164648567.3088</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>12042709012.2354</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>8502438633.82475</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>8679178145.08419</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>8931978800.39168</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>9176159249.43066</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>9443353950.50529</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>9648194015.96294</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>9833376490</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>9812114878</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>9726174631</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>9580306302</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>9554198533</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>9704286458</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>9945624071</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>10062514399</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>9905507602</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.20338329807979</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.217718735841253</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.246065370493181</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.239809308186684</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.274745773150394</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.258347640491807</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.250979014873388</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.273633430420754</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.283491993756359</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.330140487056565</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.336217130235099</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.333748231790221</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.319093753171804</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.333741192387393</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.339627936389669</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.472347731883114</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.47653385884818</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.465950798332348</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.466940112032318</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.456406384073613</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.438976928050973</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.443243792582819</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.452809302409808</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.410788258385951</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.426703245660015</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.426587881750408</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.427302669921315</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.441127002744028</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.417658099060937</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.414835106175788</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.324268970037095</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.305747405310566</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.287983831174471</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.293250579780998</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.268847842775994</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.302675431457219</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.305777192543793</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.273557267169439</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.30571974785769</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.243156267283421</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.237194988014493</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.238949098288464</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.239779244084168</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.24860070855167</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.245536957434543</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.155191376679913</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.165497267868503</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.185297732881203</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.181065654202141</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.207357069565396</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.190483692599167</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.182531352602225</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.200458681164414</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.226943761394089</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.245957121096906</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.251300472282877</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.250128342330687</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.248987793745188</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.258089129993417</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.264563599615033</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.467334020449806</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.473177590563234</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.466075156318148</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.467285928622662</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.464069182841793</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.438559146158021</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.443410457536547</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.459312454396778</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.447784685215382</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.445202107804114</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.446375978076828</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.446730278361894</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.453618787929575</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.436687487587405</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.433783964126723</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.377474602870281</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.361325141568263</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.348627110800648</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.351648417175198</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.328573747592811</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.370957161242812</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.374058189861228</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.340228864438809</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.325271553390528</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.308840771098981</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.302323549640295</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.303141379307418</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.297393418325237</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.305223382419178</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.301652436258244</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>786923.58571</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>792352.00521</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>734631.79263</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>760876.52075</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>776240.22052</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>743411.19552</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>762957.1837</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>821869.17178</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>997998.89929</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1135221.64746</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1195322.54689</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1281437.71187</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1485992.00088</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1692086.32088</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1521976.41218</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>378720.87595</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>375384.50507</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>346649.61493</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>360457.34849</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>366992.22751</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>344886.09982</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>356051.16282</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>391832.04487</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>481049.56634</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>543427.54301</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>567536.01462</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>601447.45552</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>695734.30904</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>778522.40752</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>710816.55455</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1089112.74824553</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1115849.59196854</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1147329.4202368</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>1182375.94917584</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1222559.72367744</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1260041.50260354</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>1296393.48653905</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>1326227.93547332</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1355541.9207955</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>1381600.74956218</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1409754.40131492</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>1443364.21253913</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>1487985.48051486</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
